--- a/app/templates/OT/OT-001-Geofal.xlsx
+++ b/app/templates/OT/OT-001-Geofal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\1.1 Trabajos 2026\3. Orden de Trabajo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\OT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BA789B-FF0E-41DE-B685-6B029C460A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D2E0AB-2D41-4F50-9C8D-488EB030DA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{F7990F33-BEF4-4A5A-95E9-0B9ED3C8F4A4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{F7990F33-BEF4-4A5A-95E9-0B9ED3C8F4A4}"/>
   </bookViews>
   <sheets>
     <sheet name="." sheetId="1" state="hidden" r:id="rId1"/>
@@ -179,7 +179,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="51">
   <si>
     <t>ORDEN DE TRABAJO                                                                                                                                                     DE LABORATORIO</t>
   </si>
@@ -341,19 +341,10 @@
     <t>Gravedad especifica de los solidos del suelo / ASTM D854-14</t>
   </si>
   <si>
-    <t>LÍMITE LÍQUIDO Y LÍMITE PLÁSTICO DEL SUELO  / ASTM D4318-17ε1</t>
-  </si>
-  <si>
-    <t>CONTENIDO DE HUMEDAD EN SUELOS / ASTM D2216-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">JAZMIN GRANDEZ </t>
   </si>
   <si>
     <t xml:space="preserve">BEATRIZ PARINANGO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORTE DIRECTO  </t>
   </si>
 </sst>
 </file>
@@ -607,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -672,26 +663,20 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -705,80 +690,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="171" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="171" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -787,6 +703,90 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -796,25 +796,22 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -824,21 +821,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="175" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1180,9 +1162,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1220,9 +1202,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1255,26 +1237,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1307,26 +1272,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1504,35 +1452,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" style="2" customWidth="1"/>
     <col min="11" max="11" width="18" style="2" customWidth="1"/>
-    <col min="12" max="13" width="11.42578125" style="2"/>
-    <col min="14" max="14" width="14.42578125" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="2"/>
+    <col min="12" max="13" width="11.44140625" style="2"/>
+    <col min="14" max="14" width="14.44140625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="50"/>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="60" t="s">
+    <row r="1" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1540,15 +1488,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
+    <row r="2" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
       <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1556,15 +1504,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
+    <row r="3" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
       <c r="I3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1572,15 +1520,15 @@
         <v>44774</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="50"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
+    <row r="4" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1601,14 +1549,14 @@
       <c r="J5" s="7"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" ht="34.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="58">
+      <c r="B6" s="27">
         <v>716</v>
       </c>
-      <c r="C6" s="58"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="16"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15" t="s">
@@ -1625,7 +1573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -1634,12 +1582,12 @@
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="16"/>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="59"/>
-    </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J7" s="28"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -1651,35 +1599,35 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30" t="s">
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
       <c r="J9" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>1</v>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="58">
         <v>2547</v>
       </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
       <c r="E10" s="40" t="s">
         <v>16</v>
       </c>
@@ -1691,61 +1639,61 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="12"/>
     </row>
-    <row r="12" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
-      <c r="B12" s="38">
+      <c r="B12" s="58">
         <v>2570</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
       <c r="J12" s="12"/>
     </row>
-    <row r="13" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="35"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
       <c r="J13" s="12"/>
     </row>
-    <row r="14" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="35"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="12"/>
     </row>
-    <row r="15" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
-      <c r="B15" s="47"/>
+      <c r="B15" s="52"/>
       <c r="C15" s="41"/>
       <c r="D15" s="42"/>
       <c r="E15" s="40"/>
@@ -1755,35 +1703,35 @@
       <c r="I15" s="42"/>
       <c r="J15" s="22"/>
     </row>
-    <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="35"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="33"/>
       <c r="J16" s="12"/>
     </row>
-    <row r="17" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="35"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="33"/>
       <c r="J17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
       <c r="E18" s="40"/>
       <c r="F18" s="41"/>
       <c r="G18" s="41"/>
@@ -1791,131 +1739,131 @@
       <c r="I18" s="42"/>
       <c r="J18" s="22"/>
     </row>
-    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="35"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="33"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="35"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="33"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="35"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="33"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="35"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="33"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="35"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="33"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="35"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="33"/>
       <c r="J26" s="12"/>
     </row>
-    <row r="27" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
       <c r="J27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="35"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="33"/>
       <c r="J28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
       <c r="E29" s="40"/>
       <c r="F29" s="41"/>
       <c r="G29" s="41"/>
@@ -1923,39 +1871,39 @@
       <c r="I29" s="42"/>
       <c r="J29" s="22"/>
     </row>
-    <row r="30" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="35"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="50"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
       <c r="J31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="57" t="s">
+    <row r="32" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="53">
+      <c r="B32" s="44"/>
+      <c r="C32" s="49">
         <v>45524</v>
       </c>
-      <c r="D32" s="54"/>
+      <c r="D32" s="50"/>
       <c r="E32" s="5" t="s">
         <v>19</v>
       </c>
@@ -1971,16 +1919,16 @@
       </c>
       <c r="J32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="57" t="s">
+    <row r="33" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="57"/>
-      <c r="C33" s="55">
+      <c r="B33" s="44"/>
+      <c r="C33" s="51">
         <f>+F33-F32+1</f>
         <v>14</v>
       </c>
-      <c r="D33" s="55"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="5" t="s">
         <v>23</v>
       </c>
@@ -1996,76 +1944,76 @@
       </c>
       <c r="J33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="56" t="s">
+    <row r="34" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="48" t="s">
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-    </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="48"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-    </row>
-    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="48"/>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-    </row>
-    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="48"/>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-    </row>
-    <row r="39" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="51" t="s">
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+    </row>
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="45"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+    </row>
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="45"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+    </row>
+    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="45"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+    </row>
+    <row r="39" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="52"/>
-      <c r="C39" s="47" t="s">
+      <c r="B39" s="48"/>
+      <c r="C39" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="41"/>
@@ -2074,18 +2022,61 @@
       <c r="G39" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H39" s="49" t="s">
+      <c r="H39" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-    </row>
-    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+    </row>
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H47" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:I9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:I11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:I23"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E18:I18"/>
+    <mergeCell ref="A35:J38"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:I30"/>
+    <mergeCell ref="E31:I31"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="B28:D28"/>
@@ -2102,53 +2093,10 @@
     <mergeCell ref="E25:I25"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="E21:I21"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:I29"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:I30"/>
-    <mergeCell ref="E31:I31"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A35:J38"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:I23"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:I14"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:I20"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E18:I18"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:I19"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:I11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:I12"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:I15"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="65" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
@@ -2160,35 +2108,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" style="2" customWidth="1"/>
     <col min="11" max="11" width="18" style="2" customWidth="1"/>
-    <col min="12" max="13" width="11.42578125" style="2"/>
-    <col min="14" max="14" width="14.42578125" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="2"/>
+    <col min="12" max="13" width="11.44140625" style="2"/>
+    <col min="14" max="14" width="14.44140625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="50"/>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="60" t="s">
+    <row r="1" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2196,15 +2144,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
+    <row r="2" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
       <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2212,15 +2160,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
+    <row r="3" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
       <c r="I3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2228,15 +2176,15 @@
         <v>44774</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="50"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
+    <row r="4" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>5</v>
       </c>
@@ -2257,14 +2205,14 @@
       <c r="J5" s="7"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" ht="34.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="58">
+      <c r="B6" s="27">
         <v>839</v>
       </c>
-      <c r="C6" s="58"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="16"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15" t="s">
@@ -2281,7 +2229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -2290,12 +2238,12 @@
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="16"/>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="59"/>
-    </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J7" s="28"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -2307,100 +2255,100 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30" t="s">
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
       <c r="J9" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>1</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="66" t="s">
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="71"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="62"/>
       <c r="J10" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="33" t="s">
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="35"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="66" t="s">
+      <c r="B12" s="58"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="68"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="65"/>
       <c r="J12" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="33" t="s">
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="35"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
       <c r="J13" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="47" t="s">
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="52" t="s">
         <v>37</v>
       </c>
       <c r="F14" s="41"/>
@@ -2411,91 +2359,91 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="72" t="s">
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="71"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="62"/>
       <c r="J15" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="47"/>
+      <c r="B16" s="52"/>
       <c r="C16" s="41"/>
       <c r="D16" s="42"/>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="65"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="68"/>
       <c r="J16" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
-      <c r="B17" s="47"/>
+      <c r="B17" s="52"/>
       <c r="C17" s="41"/>
       <c r="D17" s="42"/>
-      <c r="E17" s="66" t="s">
+      <c r="E17" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="68"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="65"/>
       <c r="J17" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
       <c r="E18" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="71"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="62"/>
       <c r="J18" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33" t="s">
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="35"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="33"/>
       <c r="J19" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
       <c r="E20" s="40" t="s">
         <v>43</v>
       </c>
@@ -2507,23 +2455,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
       <c r="E22" s="23"/>
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
@@ -2531,78 +2479,78 @@
       <c r="I22" s="25"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="35"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="33"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="35"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="33"/>
       <c r="J26" s="12"/>
     </row>
-    <row r="27" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
       <c r="J27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="35"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="33"/>
       <c r="J28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
       <c r="E29" s="40"/>
       <c r="F29" s="41"/>
       <c r="G29" s="41"/>
@@ -2610,39 +2558,39 @@
       <c r="I29" s="42"/>
       <c r="J29" s="22"/>
     </row>
-    <row r="30" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="35"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="50"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
       <c r="J31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="57" t="s">
+    <row r="32" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="53">
+      <c r="B32" s="44"/>
+      <c r="C32" s="49">
         <v>45555</v>
       </c>
-      <c r="D32" s="54"/>
+      <c r="D32" s="50"/>
       <c r="E32" s="5" t="s">
         <v>19</v>
       </c>
@@ -2658,16 +2606,16 @@
       </c>
       <c r="J32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="57" t="s">
+    <row r="33" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="57"/>
-      <c r="C33" s="55">
+      <c r="B33" s="44"/>
+      <c r="C33" s="51">
         <f>+F33-F32+1</f>
         <v>5</v>
       </c>
-      <c r="D33" s="55"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="5" t="s">
         <v>23</v>
       </c>
@@ -2683,76 +2631,76 @@
       </c>
       <c r="J33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="56" t="s">
+    <row r="34" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="48" t="s">
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-    </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="48"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-    </row>
-    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="48"/>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-    </row>
-    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="48"/>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-    </row>
-    <row r="39" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="51" t="s">
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+    </row>
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="45"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+    </row>
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="45"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+    </row>
+    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="45"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+    </row>
+    <row r="39" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="52"/>
-      <c r="C39" s="47" t="s">
+      <c r="B39" s="48"/>
+      <c r="C39" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="41"/>
@@ -2761,18 +2709,59 @@
       <c r="G39" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H39" s="49" t="s">
+      <c r="H39" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-    </row>
-    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+    </row>
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H47" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="E18:I18"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:I30"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:I25"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:I31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="A35:J38"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:I26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="E14:I14"/>
     <mergeCell ref="E15:I15"/>
@@ -2789,51 +2778,10 @@
     <mergeCell ref="E10:I10"/>
     <mergeCell ref="E11:I11"/>
     <mergeCell ref="E12:I12"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:I26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:I27"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:I31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="A35:J38"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="E18:I18"/>
-    <mergeCell ref="E19:I19"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:I28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:I29"/>
-    <mergeCell ref="E24:I24"/>
-    <mergeCell ref="E20:I20"/>
-    <mergeCell ref="E21:I21"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:I30"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:I25"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="65" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
@@ -2845,35 +2793,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" style="2" customWidth="1"/>
     <col min="11" max="11" width="18" style="2" customWidth="1"/>
-    <col min="12" max="13" width="11.42578125" style="2"/>
-    <col min="14" max="14" width="14.42578125" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="2"/>
+    <col min="12" max="13" width="11.44140625" style="2"/>
+    <col min="14" max="14" width="14.44140625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="50"/>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="60" t="s">
+    <row r="1" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2881,15 +2829,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
+    <row r="2" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
       <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2897,15 +2845,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
+    <row r="3" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
       <c r="I3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2913,15 +2861,15 @@
         <v>44774</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="50"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
+    <row r="4" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>5</v>
       </c>
@@ -2942,20 +2890,20 @@
       <c r="J5" s="7"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" ht="34.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="77">
+      <c r="B6" s="74">
         <v>1</v>
       </c>
-      <c r="C6" s="77"/>
+      <c r="C6" s="74"/>
       <c r="D6" s="16"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="26">
         <v>1</v>
       </c>
       <c r="H6" s="16"/>
@@ -2966,7 +2914,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -2975,12 +2923,12 @@
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="16"/>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="59"/>
-    </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J7" s="28"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -2992,333 +2940,289 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30" t="s">
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
       <c r="J9" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12">
-        <v>1</v>
-      </c>
-      <c r="B10" s="80">
-        <v>1</v>
-      </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="22"/>
+    </row>
+    <row r="11" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="22"/>
+    </row>
+    <row r="12" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="69" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="58"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="22"/>
+    </row>
+    <row r="13" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="22"/>
+    </row>
+    <row r="14" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="70"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="22"/>
+    </row>
+    <row r="15" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
-      <c r="B15" s="75"/>
-      <c r="C15" s="76"/>
-      <c r="D15" s="76"/>
-      <c r="E15" s="63" t="s">
-        <v>38</v>
-      </c>
+      <c r="B15" s="70"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="66"/>
       <c r="F15" s="41"/>
       <c r="G15" s="41"/>
       <c r="H15" s="41"/>
       <c r="I15" s="42"/>
-      <c r="J15" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J15" s="22"/>
+    </row>
+    <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="34"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="22"/>
+    </row>
+    <row r="17" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="63" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="26"/>
-      <c r="B18" s="75"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="47" t="s">
-        <v>53</v>
-      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="22"/>
+    </row>
+    <row r="18" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="52"/>
       <c r="F18" s="41"/>
       <c r="G18" s="41"/>
       <c r="H18" s="41"/>
       <c r="I18" s="42"/>
-      <c r="J18" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="27"/>
-    </row>
-    <row r="20" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J18" s="22"/>
+    </row>
+    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="22"/>
+    </row>
+    <row r="20" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="27"/>
-    </row>
-    <row r="21" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
       <c r="E21" s="69"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="27"/>
-    </row>
-    <row r="22" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="22"/>
+    </row>
+    <row r="22" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="27"/>
-    </row>
-    <row r="23" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="22"/>
+    </row>
+    <row r="23" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="27"/>
-    </row>
-    <row r="24" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="22"/>
+    </row>
+    <row r="24" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="74"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="76"/>
       <c r="J24" s="22"/>
     </row>
-    <row r="25" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
-      <c r="B25" s="75"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="27"/>
-    </row>
-    <row r="26" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="70"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="22"/>
+    </row>
+    <row r="26" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="27"/>
-    </row>
-    <row r="27" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="34"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="22"/>
+    </row>
+    <row r="27" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
       <c r="E27" s="69"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="27"/>
-    </row>
-    <row r="28" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="22"/>
+    </row>
+    <row r="28" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="27"/>
-    </row>
-    <row r="29" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="22"/>
+    </row>
+    <row r="29" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="35"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="33"/>
       <c r="J29" s="22"/>
     </row>
-    <row r="30" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="35"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
       <c r="J30" s="22"/>
     </row>
-    <row r="31" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="57" t="s">
+    <row r="31" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="57"/>
-      <c r="C31" s="53">
-        <v>46024</v>
-      </c>
-      <c r="D31" s="54"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="50"/>
       <c r="E31" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="21">
-        <v>46025</v>
-      </c>
+      <c r="F31" s="21"/>
       <c r="G31" s="5" t="s">
         <v>20</v>
       </c>
@@ -3328,22 +3232,17 @@
       </c>
       <c r="J31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="57" t="s">
+    <row r="32" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="55">
-        <f>+F32-F31+1</f>
-        <v>5</v>
-      </c>
-      <c r="D32" s="55"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F32" s="21">
-        <v>46029</v>
-      </c>
+      <c r="F32" s="21"/>
       <c r="G32" s="6" t="s">
         <v>24</v>
       </c>
@@ -3353,77 +3252,77 @@
       </c>
       <c r="J32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="56" t="s">
+    <row r="33" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="56"/>
-    </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="48" t="s">
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+    </row>
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48"/>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="48"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-    </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="48"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-    </row>
-    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="48"/>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-    </row>
-    <row r="38" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="51" t="s">
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="45"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+    </row>
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="45"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+    </row>
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="45"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+    </row>
+    <row r="38" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="52"/>
-      <c r="C38" s="47" t="s">
-        <v>51</v>
+      <c r="B38" s="48"/>
+      <c r="C38" s="52" t="s">
+        <v>49</v>
       </c>
       <c r="D38" s="41"/>
       <c r="E38" s="41"/>
@@ -3431,18 +3330,59 @@
       <c r="G38" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H38" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
-    </row>
-    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H38" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+    </row>
+    <row r="45" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H46" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="E23:I23"/>
+    <mergeCell ref="E22:I22"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A34:J37"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:I30"/>
+    <mergeCell ref="E26:I26"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:I11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:H4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:I9"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="B25:D25"/>
@@ -3459,47 +3399,6 @@
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="E20:I20"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:H4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:I30"/>
-    <mergeCell ref="E26:I26"/>
-    <mergeCell ref="E24:I24"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:I11"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:I14"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:I12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:I15"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A34:J37"/>
-    <mergeCell ref="E29:I29"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E28:I28"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E23:I23"/>
-    <mergeCell ref="E22:I22"/>
-    <mergeCell ref="E27:I27"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B26:D26"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -3515,35 +3414,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" style="2" customWidth="1"/>
     <col min="11" max="11" width="18" style="2" customWidth="1"/>
-    <col min="12" max="13" width="11.42578125" style="2"/>
-    <col min="14" max="14" width="14.42578125" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="2"/>
+    <col min="12" max="13" width="11.44140625" style="2"/>
+    <col min="14" max="14" width="14.44140625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="50"/>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="60" t="s">
+    <row r="1" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
       <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
@@ -3551,15 +3450,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
+    <row r="2" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
       <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3567,15 +3466,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
+    <row r="3" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
       <c r="I3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3583,15 +3482,15 @@
         <v>44774</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="50"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
+    <row r="4" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
       <c r="I4" s="1" t="s">
         <v>5</v>
       </c>
@@ -3612,14 +3511,14 @@
       <c r="J5" s="7"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" ht="34.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="58">
+      <c r="B6" s="27">
         <v>875</v>
       </c>
-      <c r="C6" s="58"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="16"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15" t="s">
@@ -3636,7 +3535,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -3645,12 +3544,12 @@
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="16"/>
-      <c r="I7" s="59" t="s">
+      <c r="I7" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="59"/>
-    </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J7" s="28"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -3662,100 +3561,100 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30" t="s">
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
       <c r="J9" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>1</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="66" t="s">
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="71"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="62"/>
       <c r="J10" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="33" t="s">
+      <c r="B11" s="34"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="35"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="66" t="s">
+      <c r="B12" s="58"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="68"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="65"/>
       <c r="J12" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="33" t="s">
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="35"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
       <c r="J13" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="47" t="s">
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="52" t="s">
         <v>37</v>
       </c>
       <c r="F14" s="41"/>
@@ -3766,195 +3665,195 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="72" t="s">
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="71"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="62"/>
       <c r="J15" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="63" t="s">
+      <c r="B16" s="53"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="65"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="68"/>
       <c r="J16" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
-      <c r="B17" s="47"/>
+      <c r="B17" s="52"/>
       <c r="C17" s="41"/>
       <c r="D17" s="42"/>
-      <c r="E17" s="66" t="s">
+      <c r="E17" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="68"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="65"/>
       <c r="J17" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
       <c r="E18" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="71"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="62"/>
       <c r="J18" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="35"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="33"/>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="68"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="65"/>
       <c r="J20" s="12"/>
     </row>
-    <row r="21" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="35"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="33"/>
       <c r="J21" s="12"/>
     </row>
-    <row r="22" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="65"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="68"/>
       <c r="J22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="68"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="65"/>
       <c r="J23" s="12"/>
     </row>
-    <row r="24" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="35"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="33"/>
       <c r="J24" s="12"/>
     </row>
-    <row r="25" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
       <c r="J25" s="12"/>
     </row>
-    <row r="26" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="35"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="33"/>
       <c r="J26" s="12"/>
     </row>
-    <row r="27" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
       <c r="J27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="35"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="33"/>
       <c r="J28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
       <c r="E29" s="40"/>
       <c r="F29" s="41"/>
       <c r="G29" s="41"/>
@@ -3962,39 +3861,39 @@
       <c r="I29" s="42"/>
       <c r="J29" s="22"/>
     </row>
-    <row r="30" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="35"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
       <c r="J30" s="12"/>
     </row>
-    <row r="31" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="50"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
       <c r="J31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="57" t="s">
+    <row r="32" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="53">
+      <c r="B32" s="44"/>
+      <c r="C32" s="49">
         <v>45566</v>
       </c>
-      <c r="D32" s="54"/>
+      <c r="D32" s="50"/>
       <c r="E32" s="5" t="s">
         <v>19</v>
       </c>
@@ -4010,16 +3909,16 @@
       </c>
       <c r="J32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="57" t="s">
+    <row r="33" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="57"/>
-      <c r="C33" s="55">
+      <c r="B33" s="44"/>
+      <c r="C33" s="51">
         <f>+F33-F32+1</f>
         <v>4</v>
       </c>
-      <c r="D33" s="55"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="5" t="s">
         <v>23</v>
       </c>
@@ -4035,76 +3934,76 @@
       </c>
       <c r="J33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="56" t="s">
+    <row r="34" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="48" t="s">
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-    </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="48"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-    </row>
-    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="48"/>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-    </row>
-    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="48"/>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-    </row>
-    <row r="39" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="51" t="s">
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+    </row>
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="45"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+    </row>
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="45"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+    </row>
+    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="45"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+    </row>
+    <row r="39" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="52"/>
-      <c r="C39" s="47" t="s">
+      <c r="B39" s="48"/>
+      <c r="C39" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="41"/>
@@ -4113,60 +4012,23 @@
       <c r="G39" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H39" s="49" t="s">
+      <c r="H39" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-    </row>
-    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+    </row>
+    <row r="46" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H47" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:H4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:I9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:I11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:I12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:I13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:I15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:I18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:I19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:I20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:I21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:I23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:I25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:I26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:J38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="H39:J39"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:I28"/>
@@ -4179,15 +4041,52 @@
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:J38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:I25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:I26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:I23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:I18"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:I13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:I11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:H4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:I9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="65" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="63" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
